--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:J13"/>
+  <dimension ref="A1:R13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -434,35 +434,75 @@
       </c>
       <c r="D1" t="inlineStr">
         <is>
+          <t>Hidden</t>
+        </is>
+      </c>
+      <c r="E1" t="inlineStr">
+        <is>
+          <t>LR</t>
+        </is>
+      </c>
+      <c r="F1" t="inlineStr">
+        <is>
+          <t>Dropout</t>
+        </is>
+      </c>
+      <c r="G1" t="inlineStr">
+        <is>
+          <t>Weight_Decay</t>
+        </is>
+      </c>
+      <c r="H1" t="inlineStr">
+        <is>
+          <t>Epochs</t>
+        </is>
+      </c>
+      <c r="I1" t="inlineStr">
+        <is>
           <t>AUC</t>
         </is>
       </c>
-      <c r="E1" t="inlineStr">
+      <c r="J1" t="inlineStr">
         <is>
           <t>Average_Precision</t>
         </is>
       </c>
-      <c r="F1" t="inlineStr">
+      <c r="K1" t="inlineStr">
         <is>
           <t>F1</t>
         </is>
       </c>
-      <c r="G1" t="inlineStr">
+      <c r="L1" t="inlineStr">
         <is>
           <t>Hits@K</t>
         </is>
       </c>
-      <c r="H1" t="inlineStr">
+      <c r="M1" t="inlineStr">
+        <is>
+          <t>Common_Neighbors</t>
+        </is>
+      </c>
+      <c r="N1" t="inlineStr">
+        <is>
+          <t>Adamic_Adar</t>
+        </is>
+      </c>
+      <c r="O1" t="inlineStr">
+        <is>
+          <t>Preferential_Attachment</t>
+        </is>
+      </c>
+      <c r="P1" t="inlineStr">
         <is>
           <t>Training_Time</t>
         </is>
       </c>
-      <c r="I1" t="inlineStr">
+      <c r="Q1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="J1" t="inlineStr">
+      <c r="R1" t="inlineStr">
         <is>
           <t>Memory_MB</t>
         </is>
@@ -485,25 +525,49 @@
         </is>
       </c>
       <c r="D2" t="n">
-        <v>0.766</v>
+        <v>32</v>
       </c>
       <c r="E2" t="n">
-        <v>0.745</v>
+        <v>0.01</v>
       </c>
       <c r="F2" t="n">
-        <v>0.7282999999999999</v>
+        <v>0.5</v>
       </c>
       <c r="G2" t="n">
-        <v>0.6583</v>
+        <v>0.0005</v>
       </c>
       <c r="H2" t="n">
-        <v>1.77</v>
+        <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>46944</v>
+        <v>0.7771</v>
       </c>
       <c r="J2" t="n">
-        <v>369.59</v>
+        <v>0.7912</v>
+      </c>
+      <c r="K2" t="n">
+        <v>0.7252999999999999</v>
+      </c>
+      <c r="L2" t="n">
+        <v>0.6422</v>
+      </c>
+      <c r="M2" t="n">
+        <v>0</v>
+      </c>
+      <c r="N2" t="n">
+        <v>0</v>
+      </c>
+      <c r="O2" t="n">
+        <v>6</v>
+      </c>
+      <c r="P2" t="n">
+        <v>1.9</v>
+      </c>
+      <c r="Q2" t="n">
+        <v>47008</v>
+      </c>
+      <c r="R2" t="n">
+        <v>382.33</v>
       </c>
     </row>
     <row r="3">
@@ -523,25 +587,49 @@
         </is>
       </c>
       <c r="D3" t="n">
-        <v>0.8602</v>
+        <v>32</v>
       </c>
       <c r="E3" t="n">
-        <v>0.8712</v>
+        <v>0.01</v>
       </c>
       <c r="F3" t="n">
-        <v>0.7569</v>
+        <v>0.5</v>
       </c>
       <c r="G3" t="n">
-        <v>0.7109</v>
+        <v>0.0005</v>
       </c>
       <c r="H3" t="n">
-        <v>5.47</v>
+        <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>375904</v>
+        <v>0.8308</v>
       </c>
       <c r="J3" t="n">
-        <v>451.2</v>
+        <v>0.8472</v>
+      </c>
+      <c r="K3" t="n">
+        <v>0.7431</v>
+      </c>
+      <c r="L3" t="n">
+        <v>0.7104</v>
+      </c>
+      <c r="M3" t="n">
+        <v>0</v>
+      </c>
+      <c r="N3" t="n">
+        <v>0</v>
+      </c>
+      <c r="O3" t="n">
+        <v>6</v>
+      </c>
+      <c r="P3" t="n">
+        <v>5.5</v>
+      </c>
+      <c r="Q3" t="n">
+        <v>376416</v>
+      </c>
+      <c r="R3" t="n">
+        <v>464.3</v>
       </c>
     </row>
     <row r="4">
@@ -561,25 +649,49 @@
         </is>
       </c>
       <c r="D4" t="n">
-        <v>0.7642</v>
+        <v>32</v>
       </c>
       <c r="E4" t="n">
-        <v>0.7481</v>
+        <v>0.01</v>
       </c>
       <c r="F4" t="n">
-        <v>0.7264</v>
+        <v>0.5</v>
       </c>
       <c r="G4" t="n">
-        <v>0.6899999999999999</v>
+        <v>0.0005</v>
       </c>
       <c r="H4" t="n">
-        <v>3.21</v>
+        <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>93824</v>
+        <v>0.7539</v>
       </c>
       <c r="J4" t="n">
-        <v>451.95</v>
+        <v>0.7393999999999999</v>
+      </c>
+      <c r="K4" t="n">
+        <v>0.7136</v>
+      </c>
+      <c r="L4" t="n">
+        <v>0.6251</v>
+      </c>
+      <c r="M4" t="n">
+        <v>0</v>
+      </c>
+      <c r="N4" t="n">
+        <v>0</v>
+      </c>
+      <c r="O4" t="n">
+        <v>6</v>
+      </c>
+      <c r="P4" t="n">
+        <v>3.28</v>
+      </c>
+      <c r="Q4" t="n">
+        <v>93888</v>
+      </c>
+      <c r="R4" t="n">
+        <v>465.3</v>
       </c>
     </row>
     <row r="5">
@@ -599,25 +711,49 @@
         </is>
       </c>
       <c r="D5" t="n">
-        <v>0.7119</v>
+        <v>32</v>
       </c>
       <c r="E5" t="n">
-        <v>0.6997</v>
+        <v>0.01</v>
       </c>
       <c r="F5" t="n">
-        <v>0.6797</v>
+        <v>0.5</v>
       </c>
       <c r="G5" t="n">
-        <v>0.6379</v>
+        <v>0.0005</v>
       </c>
       <c r="H5" t="n">
-        <v>3.19</v>
+        <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>49056</v>
+        <v>0.8306</v>
       </c>
       <c r="J5" t="n">
-        <v>435.68</v>
+        <v>0.8408</v>
+      </c>
+      <c r="K5" t="n">
+        <v>0.7607</v>
+      </c>
+      <c r="L5" t="n">
+        <v>0.6725</v>
+      </c>
+      <c r="M5" t="n">
+        <v>0</v>
+      </c>
+      <c r="N5" t="n">
+        <v>0</v>
+      </c>
+      <c r="O5" t="n">
+        <v>6</v>
+      </c>
+      <c r="P5" t="n">
+        <v>3.11</v>
+      </c>
+      <c r="Q5" t="n">
+        <v>48064</v>
+      </c>
+      <c r="R5" t="n">
+        <v>448.16</v>
       </c>
     </row>
     <row r="6">
@@ -637,25 +773,49 @@
         </is>
       </c>
       <c r="D6" t="n">
-        <v>0.8075</v>
+        <v>32</v>
       </c>
       <c r="E6" t="n">
-        <v>0.8047</v>
+        <v>0.01</v>
       </c>
       <c r="F6" t="n">
-        <v>0.7365</v>
+        <v>0.5</v>
       </c>
       <c r="G6" t="n">
-        <v>0.6967</v>
+        <v>0.0005</v>
       </c>
       <c r="H6" t="n">
-        <v>2.8</v>
+        <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>119584</v>
+        <v>0.7993</v>
       </c>
       <c r="J6" t="n">
-        <v>398.4</v>
+        <v>0.8097</v>
+      </c>
+      <c r="K6" t="n">
+        <v>0.7316</v>
+      </c>
+      <c r="L6" t="n">
+        <v>0.6341</v>
+      </c>
+      <c r="M6" t="n">
+        <v>0</v>
+      </c>
+      <c r="N6" t="n">
+        <v>0</v>
+      </c>
+      <c r="O6" t="n">
+        <v>0</v>
+      </c>
+      <c r="P6" t="n">
+        <v>2.87</v>
+      </c>
+      <c r="Q6" t="n">
+        <v>119648</v>
+      </c>
+      <c r="R6" t="n">
+        <v>412.72</v>
       </c>
     </row>
     <row r="7">
@@ -675,25 +835,49 @@
         </is>
       </c>
       <c r="D7" t="n">
-        <v>0.8773</v>
+        <v>32</v>
       </c>
       <c r="E7" t="n">
-        <v>0.8897</v>
+        <v>0.01</v>
       </c>
       <c r="F7" t="n">
-        <v>0.7624</v>
+        <v>0.5</v>
       </c>
       <c r="G7" t="n">
-        <v>0.7209</v>
+        <v>0.0005</v>
       </c>
       <c r="H7" t="n">
-        <v>8.449999999999999</v>
+        <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>957024</v>
+        <v>0.8806</v>
       </c>
       <c r="J7" t="n">
-        <v>472.88</v>
+        <v>0.8975</v>
+      </c>
+      <c r="K7" t="n">
+        <v>0.7632</v>
+      </c>
+      <c r="L7" t="n">
+        <v>0.711</v>
+      </c>
+      <c r="M7" t="n">
+        <v>0</v>
+      </c>
+      <c r="N7" t="n">
+        <v>0</v>
+      </c>
+      <c r="O7" t="n">
+        <v>0</v>
+      </c>
+      <c r="P7" t="n">
+        <v>8.300000000000001</v>
+      </c>
+      <c r="Q7" t="n">
+        <v>957536</v>
+      </c>
+      <c r="R7" t="n">
+        <v>483.75</v>
       </c>
     </row>
     <row r="8">
@@ -713,25 +897,49 @@
         </is>
       </c>
       <c r="D8" t="n">
-        <v>0.7408</v>
+        <v>32</v>
       </c>
       <c r="E8" t="n">
-        <v>0.7272</v>
+        <v>0.01</v>
       </c>
       <c r="F8" t="n">
-        <v>0.7093</v>
+        <v>0.5</v>
       </c>
       <c r="G8" t="n">
-        <v>0.6588000000000001</v>
+        <v>0.0005</v>
       </c>
       <c r="H8" t="n">
-        <v>7.25</v>
+        <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>239104</v>
+        <v>0.7716</v>
       </c>
       <c r="J8" t="n">
-        <v>608.66</v>
+        <v>0.768</v>
+      </c>
+      <c r="K8" t="n">
+        <v>0.7173</v>
+      </c>
+      <c r="L8" t="n">
+        <v>0.6352</v>
+      </c>
+      <c r="M8" t="n">
+        <v>0</v>
+      </c>
+      <c r="N8" t="n">
+        <v>0</v>
+      </c>
+      <c r="O8" t="n">
+        <v>0</v>
+      </c>
+      <c r="P8" t="n">
+        <v>7.13</v>
+      </c>
+      <c r="Q8" t="n">
+        <v>239168</v>
+      </c>
+      <c r="R8" t="n">
+        <v>621.73</v>
       </c>
     </row>
     <row r="9">
@@ -751,25 +959,49 @@
         </is>
       </c>
       <c r="D9" t="n">
-        <v>0.7272999999999999</v>
+        <v>32</v>
       </c>
       <c r="E9" t="n">
-        <v>0.6934</v>
+        <v>0.01</v>
       </c>
       <c r="F9" t="n">
-        <v>0.6938</v>
+        <v>0.5</v>
       </c>
       <c r="G9" t="n">
-        <v>0.5121</v>
+        <v>0.0005</v>
       </c>
       <c r="H9" t="n">
-        <v>7.12</v>
+        <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>121696</v>
+        <v>0.7779</v>
       </c>
       <c r="J9" t="n">
-        <v>593.36</v>
+        <v>0.7665999999999999</v>
+      </c>
+      <c r="K9" t="n">
+        <v>0.7482</v>
+      </c>
+      <c r="L9" t="n">
+        <v>0.6412</v>
+      </c>
+      <c r="M9" t="n">
+        <v>0</v>
+      </c>
+      <c r="N9" t="n">
+        <v>0</v>
+      </c>
+      <c r="O9" t="n">
+        <v>0</v>
+      </c>
+      <c r="P9" t="n">
+        <v>6.84</v>
+      </c>
+      <c r="Q9" t="n">
+        <v>120704</v>
+      </c>
+      <c r="R9" t="n">
+        <v>605.86</v>
       </c>
     </row>
     <row r="10">
@@ -789,25 +1021,49 @@
         </is>
       </c>
       <c r="D10" t="n">
-        <v>0.9406</v>
+        <v>32</v>
       </c>
       <c r="E10" t="n">
-        <v>0.9443</v>
+        <v>0.01</v>
       </c>
       <c r="F10" t="n">
-        <v>0.7892</v>
+        <v>0.5</v>
       </c>
       <c r="G10" t="n">
-        <v>0.7357</v>
+        <v>0.0005</v>
       </c>
       <c r="H10" t="n">
-        <v>5.38</v>
+        <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>17088</v>
+        <v>0.9162</v>
       </c>
       <c r="J10" t="n">
-        <v>452.04</v>
+        <v>0.9291</v>
+      </c>
+      <c r="K10" t="n">
+        <v>0.7879</v>
+      </c>
+      <c r="L10" t="n">
+        <v>0.6961000000000001</v>
+      </c>
+      <c r="M10" t="n">
+        <v>0</v>
+      </c>
+      <c r="N10" t="n">
+        <v>0</v>
+      </c>
+      <c r="O10" t="n">
+        <v>12</v>
+      </c>
+      <c r="P10" t="n">
+        <v>5.68</v>
+      </c>
+      <c r="Q10" t="n">
+        <v>17152</v>
+      </c>
+      <c r="R10" t="n">
+        <v>482.62</v>
       </c>
     </row>
     <row r="11">
@@ -827,25 +1083,49 @@
         </is>
       </c>
       <c r="D11" t="n">
-        <v>0.9028</v>
+        <v>32</v>
       </c>
       <c r="E11" t="n">
-        <v>0.8865</v>
+        <v>0.01</v>
       </c>
       <c r="F11" t="n">
-        <v>0.8052</v>
+        <v>0.5</v>
       </c>
       <c r="G11" t="n">
-        <v>0.708</v>
+        <v>0.0005</v>
       </c>
       <c r="H11" t="n">
-        <v>26.48</v>
+        <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>137056</v>
+        <v>0.9286</v>
       </c>
       <c r="J11" t="n">
-        <v>846.8200000000001</v>
+        <v>0.9283</v>
+      </c>
+      <c r="K11" t="n">
+        <v>0.7941</v>
+      </c>
+      <c r="L11" t="n">
+        <v>0.7191</v>
+      </c>
+      <c r="M11" t="n">
+        <v>0</v>
+      </c>
+      <c r="N11" t="n">
+        <v>0</v>
+      </c>
+      <c r="O11" t="n">
+        <v>12</v>
+      </c>
+      <c r="P11" t="n">
+        <v>26.59</v>
+      </c>
+      <c r="Q11" t="n">
+        <v>137568</v>
+      </c>
+      <c r="R11" t="n">
+        <v>829.01</v>
       </c>
     </row>
     <row r="12">
@@ -865,25 +1145,49 @@
         </is>
       </c>
       <c r="D12" t="n">
-        <v>0.8436</v>
+        <v>32</v>
       </c>
       <c r="E12" t="n">
-        <v>0.8526</v>
+        <v>0.01</v>
       </c>
       <c r="F12" t="n">
-        <v>0.7548</v>
+        <v>0.5</v>
       </c>
       <c r="G12" t="n">
-        <v>0.6958</v>
+        <v>0.0005</v>
       </c>
       <c r="H12" t="n">
-        <v>8.859999999999999</v>
+        <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>34112</v>
+        <v>0.8182</v>
       </c>
       <c r="J12" t="n">
-        <v>618.26</v>
+        <v>0.8234</v>
+      </c>
+      <c r="K12" t="n">
+        <v>0.7389</v>
+      </c>
+      <c r="L12" t="n">
+        <v>0.6441</v>
+      </c>
+      <c r="M12" t="n">
+        <v>0</v>
+      </c>
+      <c r="N12" t="n">
+        <v>0</v>
+      </c>
+      <c r="O12" t="n">
+        <v>12</v>
+      </c>
+      <c r="P12" t="n">
+        <v>8.93</v>
+      </c>
+      <c r="Q12" t="n">
+        <v>34176</v>
+      </c>
+      <c r="R12" t="n">
+        <v>646.27</v>
       </c>
     </row>
     <row r="13">
@@ -903,25 +1207,49 @@
         </is>
       </c>
       <c r="D13" t="n">
-        <v>0.823</v>
+        <v>32</v>
       </c>
       <c r="E13" t="n">
-        <v>0.8685</v>
+        <v>0.01</v>
       </c>
       <c r="F13" t="n">
-        <v>0.7297</v>
+        <v>0.5</v>
       </c>
       <c r="G13" t="n">
-        <v>0.6438</v>
+        <v>0.0005</v>
       </c>
       <c r="H13" t="n">
-        <v>9.26</v>
+        <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>19200</v>
+        <v>0.8759</v>
       </c>
       <c r="J13" t="n">
-        <v>574.15</v>
+        <v>0.8986</v>
+      </c>
+      <c r="K13" t="n">
+        <v>0.7607</v>
+      </c>
+      <c r="L13" t="n">
+        <v>0.6832</v>
+      </c>
+      <c r="M13" t="n">
+        <v>0</v>
+      </c>
+      <c r="N13" t="n">
+        <v>0</v>
+      </c>
+      <c r="O13" t="n">
+        <v>12</v>
+      </c>
+      <c r="P13" t="n">
+        <v>8.800000000000001</v>
+      </c>
+      <c r="Q13" t="n">
+        <v>18208</v>
+      </c>
+      <c r="R13" t="n">
+        <v>601.8099999999999</v>
       </c>
     </row>
   </sheetData>

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -540,34 +540,34 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7771</v>
+        <v>0.7836</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7912</v>
+        <v>0.7914</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7252999999999999</v>
+        <v>0.7236</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6422</v>
+        <v>0.6815</v>
       </c>
       <c r="M2" t="n">
-        <v>0</v>
+        <v>0.2748</v>
       </c>
       <c r="N2" t="n">
-        <v>0</v>
+        <v>0.1926</v>
       </c>
       <c r="O2" t="n">
-        <v>6</v>
+        <v>24.6452</v>
       </c>
       <c r="P2" t="n">
-        <v>1.9</v>
+        <v>3.46</v>
       </c>
       <c r="Q2" t="n">
         <v>47008</v>
       </c>
       <c r="R2" t="n">
-        <v>382.33</v>
+        <v>389.55</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:R13"/>
+  <dimension ref="A1:AD13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -507,6 +507,66 @@
           <t>Memory_MB</t>
         </is>
       </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>CN_AUC</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>CN_Average_Precision</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>CN_F1</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>CN_Hits@K</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>AA_AUC</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>AA_Average_Precision</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
+          <t>AA_F1</t>
+        </is>
+      </c>
+      <c r="Z1" t="inlineStr">
+        <is>
+          <t>AA_Hits@K</t>
+        </is>
+      </c>
+      <c r="AA1" t="inlineStr">
+        <is>
+          <t>PA_AUC</t>
+        </is>
+      </c>
+      <c r="AB1" t="inlineStr">
+        <is>
+          <t>PA_Average_Precision</t>
+        </is>
+      </c>
+      <c r="AC1" t="inlineStr">
+        <is>
+          <t>PA_F1</t>
+        </is>
+      </c>
+      <c r="AD1" t="inlineStr">
+        <is>
+          <t>PA_Hits@K</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
@@ -540,16 +600,16 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7836</v>
+        <v>0.7886</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7914</v>
+        <v>0.8027</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7236</v>
+        <v>0.7204</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6815</v>
+        <v>0.6711</v>
       </c>
       <c r="M2" t="n">
         <v>0.2748</v>
@@ -561,13 +621,49 @@
         <v>24.6452</v>
       </c>
       <c r="P2" t="n">
-        <v>3.46</v>
+        <v>1.07</v>
       </c>
       <c r="Q2" t="n">
-        <v>47008</v>
+        <v>48064</v>
       </c>
       <c r="R2" t="n">
-        <v>389.55</v>
+        <v>390.86</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="T2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="V2" t="n">
+        <v>1</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="X2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="Z2" t="n">
+        <v>1</v>
+      </c>
+      <c r="AA2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AB2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="AC2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="AD2" t="n">
+        <v>1</v>
       </c>
     </row>
     <row r="3">
@@ -631,6 +727,18 @@
       <c r="R3" t="n">
         <v>464.3</v>
       </c>
+      <c r="S3" t="inlineStr"/>
+      <c r="T3" t="inlineStr"/>
+      <c r="U3" t="inlineStr"/>
+      <c r="V3" t="inlineStr"/>
+      <c r="W3" t="inlineStr"/>
+      <c r="X3" t="inlineStr"/>
+      <c r="Y3" t="inlineStr"/>
+      <c r="Z3" t="inlineStr"/>
+      <c r="AA3" t="inlineStr"/>
+      <c r="AB3" t="inlineStr"/>
+      <c r="AC3" t="inlineStr"/>
+      <c r="AD3" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -693,6 +801,18 @@
       <c r="R4" t="n">
         <v>465.3</v>
       </c>
+      <c r="S4" t="inlineStr"/>
+      <c r="T4" t="inlineStr"/>
+      <c r="U4" t="inlineStr"/>
+      <c r="V4" t="inlineStr"/>
+      <c r="W4" t="inlineStr"/>
+      <c r="X4" t="inlineStr"/>
+      <c r="Y4" t="inlineStr"/>
+      <c r="Z4" t="inlineStr"/>
+      <c r="AA4" t="inlineStr"/>
+      <c r="AB4" t="inlineStr"/>
+      <c r="AC4" t="inlineStr"/>
+      <c r="AD4" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -755,6 +875,18 @@
       <c r="R5" t="n">
         <v>448.16</v>
       </c>
+      <c r="S5" t="inlineStr"/>
+      <c r="T5" t="inlineStr"/>
+      <c r="U5" t="inlineStr"/>
+      <c r="V5" t="inlineStr"/>
+      <c r="W5" t="inlineStr"/>
+      <c r="X5" t="inlineStr"/>
+      <c r="Y5" t="inlineStr"/>
+      <c r="Z5" t="inlineStr"/>
+      <c r="AA5" t="inlineStr"/>
+      <c r="AB5" t="inlineStr"/>
+      <c r="AC5" t="inlineStr"/>
+      <c r="AD5" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -817,6 +949,18 @@
       <c r="R6" t="n">
         <v>412.72</v>
       </c>
+      <c r="S6" t="inlineStr"/>
+      <c r="T6" t="inlineStr"/>
+      <c r="U6" t="inlineStr"/>
+      <c r="V6" t="inlineStr"/>
+      <c r="W6" t="inlineStr"/>
+      <c r="X6" t="inlineStr"/>
+      <c r="Y6" t="inlineStr"/>
+      <c r="Z6" t="inlineStr"/>
+      <c r="AA6" t="inlineStr"/>
+      <c r="AB6" t="inlineStr"/>
+      <c r="AC6" t="inlineStr"/>
+      <c r="AD6" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -879,6 +1023,18 @@
       <c r="R7" t="n">
         <v>483.75</v>
       </c>
+      <c r="S7" t="inlineStr"/>
+      <c r="T7" t="inlineStr"/>
+      <c r="U7" t="inlineStr"/>
+      <c r="V7" t="inlineStr"/>
+      <c r="W7" t="inlineStr"/>
+      <c r="X7" t="inlineStr"/>
+      <c r="Y7" t="inlineStr"/>
+      <c r="Z7" t="inlineStr"/>
+      <c r="AA7" t="inlineStr"/>
+      <c r="AB7" t="inlineStr"/>
+      <c r="AC7" t="inlineStr"/>
+      <c r="AD7" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -941,6 +1097,18 @@
       <c r="R8" t="n">
         <v>621.73</v>
       </c>
+      <c r="S8" t="inlineStr"/>
+      <c r="T8" t="inlineStr"/>
+      <c r="U8" t="inlineStr"/>
+      <c r="V8" t="inlineStr"/>
+      <c r="W8" t="inlineStr"/>
+      <c r="X8" t="inlineStr"/>
+      <c r="Y8" t="inlineStr"/>
+      <c r="Z8" t="inlineStr"/>
+      <c r="AA8" t="inlineStr"/>
+      <c r="AB8" t="inlineStr"/>
+      <c r="AC8" t="inlineStr"/>
+      <c r="AD8" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1003,6 +1171,18 @@
       <c r="R9" t="n">
         <v>605.86</v>
       </c>
+      <c r="S9" t="inlineStr"/>
+      <c r="T9" t="inlineStr"/>
+      <c r="U9" t="inlineStr"/>
+      <c r="V9" t="inlineStr"/>
+      <c r="W9" t="inlineStr"/>
+      <c r="X9" t="inlineStr"/>
+      <c r="Y9" t="inlineStr"/>
+      <c r="Z9" t="inlineStr"/>
+      <c r="AA9" t="inlineStr"/>
+      <c r="AB9" t="inlineStr"/>
+      <c r="AC9" t="inlineStr"/>
+      <c r="AD9" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1065,6 +1245,18 @@
       <c r="R10" t="n">
         <v>482.62</v>
       </c>
+      <c r="S10" t="inlineStr"/>
+      <c r="T10" t="inlineStr"/>
+      <c r="U10" t="inlineStr"/>
+      <c r="V10" t="inlineStr"/>
+      <c r="W10" t="inlineStr"/>
+      <c r="X10" t="inlineStr"/>
+      <c r="Y10" t="inlineStr"/>
+      <c r="Z10" t="inlineStr"/>
+      <c r="AA10" t="inlineStr"/>
+      <c r="AB10" t="inlineStr"/>
+      <c r="AC10" t="inlineStr"/>
+      <c r="AD10" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1127,6 +1319,18 @@
       <c r="R11" t="n">
         <v>829.01</v>
       </c>
+      <c r="S11" t="inlineStr"/>
+      <c r="T11" t="inlineStr"/>
+      <c r="U11" t="inlineStr"/>
+      <c r="V11" t="inlineStr"/>
+      <c r="W11" t="inlineStr"/>
+      <c r="X11" t="inlineStr"/>
+      <c r="Y11" t="inlineStr"/>
+      <c r="Z11" t="inlineStr"/>
+      <c r="AA11" t="inlineStr"/>
+      <c r="AB11" t="inlineStr"/>
+      <c r="AC11" t="inlineStr"/>
+      <c r="AD11" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1189,6 +1393,18 @@
       <c r="R12" t="n">
         <v>646.27</v>
       </c>
+      <c r="S12" t="inlineStr"/>
+      <c r="T12" t="inlineStr"/>
+      <c r="U12" t="inlineStr"/>
+      <c r="V12" t="inlineStr"/>
+      <c r="W12" t="inlineStr"/>
+      <c r="X12" t="inlineStr"/>
+      <c r="Y12" t="inlineStr"/>
+      <c r="Z12" t="inlineStr"/>
+      <c r="AA12" t="inlineStr"/>
+      <c r="AB12" t="inlineStr"/>
+      <c r="AC12" t="inlineStr"/>
+      <c r="AD12" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1251,6 +1467,18 @@
       <c r="R13" t="n">
         <v>601.8099999999999</v>
       </c>
+      <c r="S13" t="inlineStr"/>
+      <c r="T13" t="inlineStr"/>
+      <c r="U13" t="inlineStr"/>
+      <c r="V13" t="inlineStr"/>
+      <c r="W13" t="inlineStr"/>
+      <c r="X13" t="inlineStr"/>
+      <c r="Y13" t="inlineStr"/>
+      <c r="Z13" t="inlineStr"/>
+      <c r="AA13" t="inlineStr"/>
+      <c r="AB13" t="inlineStr"/>
+      <c r="AC13" t="inlineStr"/>
+      <c r="AD13" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AD13"/>
+  <dimension ref="A1:AA13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -479,92 +479,77 @@
       </c>
       <c r="M1" t="inlineStr">
         <is>
-          <t>Common_Neighbors</t>
+          <t>CN_AUC</t>
         </is>
       </c>
       <c r="N1" t="inlineStr">
         <is>
-          <t>Adamic_Adar</t>
+          <t>CN_Average_Precision</t>
         </is>
       </c>
       <c r="O1" t="inlineStr">
         <is>
-          <t>Preferential_Attachment</t>
+          <t>CN_F1</t>
         </is>
       </c>
       <c r="P1" t="inlineStr">
         <is>
+          <t>CN_Hits@K</t>
+        </is>
+      </c>
+      <c r="Q1" t="inlineStr">
+        <is>
+          <t>AA_AUC</t>
+        </is>
+      </c>
+      <c r="R1" t="inlineStr">
+        <is>
+          <t>AA_Average_Precision</t>
+        </is>
+      </c>
+      <c r="S1" t="inlineStr">
+        <is>
+          <t>AA_F1</t>
+        </is>
+      </c>
+      <c r="T1" t="inlineStr">
+        <is>
+          <t>AA_Hits@K</t>
+        </is>
+      </c>
+      <c r="U1" t="inlineStr">
+        <is>
+          <t>PA_AUC</t>
+        </is>
+      </c>
+      <c r="V1" t="inlineStr">
+        <is>
+          <t>PA_Average_Precision</t>
+        </is>
+      </c>
+      <c r="W1" t="inlineStr">
+        <is>
+          <t>PA_F1</t>
+        </is>
+      </c>
+      <c r="X1" t="inlineStr">
+        <is>
+          <t>PA_Hits@K</t>
+        </is>
+      </c>
+      <c r="Y1" t="inlineStr">
+        <is>
           <t>Training_Time</t>
         </is>
       </c>
-      <c r="Q1" t="inlineStr">
+      <c r="Z1" t="inlineStr">
         <is>
           <t>Parameters</t>
         </is>
       </c>
-      <c r="R1" t="inlineStr">
+      <c r="AA1" t="inlineStr">
         <is>
           <t>Memory_MB</t>
-        </is>
-      </c>
-      <c r="S1" t="inlineStr">
-        <is>
-          <t>CN_AUC</t>
-        </is>
-      </c>
-      <c r="T1" t="inlineStr">
-        <is>
-          <t>CN_Average_Precision</t>
-        </is>
-      </c>
-      <c r="U1" t="inlineStr">
-        <is>
-          <t>CN_F1</t>
-        </is>
-      </c>
-      <c r="V1" t="inlineStr">
-        <is>
-          <t>CN_Hits@K</t>
-        </is>
-      </c>
-      <c r="W1" t="inlineStr">
-        <is>
-          <t>AA_AUC</t>
-        </is>
-      </c>
-      <c r="X1" t="inlineStr">
-        <is>
-          <t>AA_Average_Precision</t>
-        </is>
-      </c>
-      <c r="Y1" t="inlineStr">
-        <is>
-          <t>AA_F1</t>
-        </is>
-      </c>
-      <c r="Z1" t="inlineStr">
-        <is>
-          <t>AA_Hits@K</t>
-        </is>
-      </c>
-      <c r="AA1" t="inlineStr">
-        <is>
-          <t>PA_AUC</t>
-        </is>
-      </c>
-      <c r="AB1" t="inlineStr">
-        <is>
-          <t>PA_Average_Precision</t>
-        </is>
-      </c>
-      <c r="AC1" t="inlineStr">
-        <is>
-          <t>PA_F1</t>
-        </is>
-      </c>
-      <c r="AD1" t="inlineStr">
-        <is>
-          <t>PA_Hits@K</t>
         </is>
       </c>
     </row>
@@ -612,58 +597,49 @@
         <v>0.6711</v>
       </c>
       <c r="M2" t="n">
-        <v>0.2748</v>
+        <v>0.5</v>
       </c>
       <c r="N2" t="n">
-        <v>0.1926</v>
+        <v>0.5</v>
       </c>
       <c r="O2" t="n">
-        <v>24.6452</v>
+        <v>0.6667</v>
       </c>
       <c r="P2" t="n">
-        <v>1.07</v>
+        <v>1</v>
       </c>
       <c r="Q2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T2" t="n">
+        <v>1</v>
+      </c>
+      <c r="U2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V2" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W2" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X2" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y2" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="Z2" t="n">
         <v>48064</v>
       </c>
-      <c r="R2" t="n">
-        <v>390.86</v>
-      </c>
-      <c r="S2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="T2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="U2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="V2" t="n">
-        <v>1</v>
-      </c>
-      <c r="W2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="X2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="Y2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="Z2" t="n">
-        <v>1</v>
-      </c>
       <c r="AA2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AB2" t="n">
-        <v>0.5</v>
-      </c>
-      <c r="AC2" t="n">
-        <v>0.6667</v>
-      </c>
-      <c r="AD2" t="n">
-        <v>1</v>
+        <v>384.54</v>
       </c>
     </row>
     <row r="3">
@@ -698,47 +674,62 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8308</v>
+        <v>0.8866000000000001</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8472</v>
+        <v>0.8917</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7431</v>
+        <v>0.7736</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7104</v>
+        <v>0.7227</v>
       </c>
       <c r="M3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N3" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O3" t="n">
-        <v>6</v>
+        <v>0.6667</v>
       </c>
       <c r="P3" t="n">
-        <v>5.5</v>
+        <v>1</v>
       </c>
       <c r="Q3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T3" t="n">
+        <v>1</v>
+      </c>
+      <c r="U3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V3" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W3" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X3" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y3" t="n">
+        <v>2.66</v>
+      </c>
+      <c r="Z3" t="n">
         <v>376416</v>
       </c>
-      <c r="R3" t="n">
-        <v>464.3</v>
-      </c>
-      <c r="S3" t="inlineStr"/>
-      <c r="T3" t="inlineStr"/>
-      <c r="U3" t="inlineStr"/>
-      <c r="V3" t="inlineStr"/>
-      <c r="W3" t="inlineStr"/>
-      <c r="X3" t="inlineStr"/>
-      <c r="Y3" t="inlineStr"/>
-      <c r="Z3" t="inlineStr"/>
-      <c r="AA3" t="inlineStr"/>
-      <c r="AB3" t="inlineStr"/>
-      <c r="AC3" t="inlineStr"/>
-      <c r="AD3" t="inlineStr"/>
+      <c r="AA3" t="n">
+        <v>470.86</v>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
@@ -772,47 +763,62 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7539</v>
+        <v>0.7875</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7393999999999999</v>
+        <v>0.7818000000000001</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7136</v>
+        <v>0.7388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6251</v>
+        <v>0.6649</v>
       </c>
       <c r="M4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N4" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O4" t="n">
-        <v>6</v>
+        <v>0.6667</v>
       </c>
       <c r="P4" t="n">
-        <v>3.28</v>
+        <v>1</v>
       </c>
       <c r="Q4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T4" t="n">
+        <v>1</v>
+      </c>
+      <c r="U4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V4" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W4" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X4" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y4" t="n">
+        <v>1.65</v>
+      </c>
+      <c r="Z4" t="n">
         <v>93888</v>
       </c>
-      <c r="R4" t="n">
-        <v>465.3</v>
-      </c>
-      <c r="S4" t="inlineStr"/>
-      <c r="T4" t="inlineStr"/>
-      <c r="U4" t="inlineStr"/>
-      <c r="V4" t="inlineStr"/>
-      <c r="W4" t="inlineStr"/>
-      <c r="X4" t="inlineStr"/>
-      <c r="Y4" t="inlineStr"/>
-      <c r="Z4" t="inlineStr"/>
-      <c r="AA4" t="inlineStr"/>
-      <c r="AB4" t="inlineStr"/>
-      <c r="AC4" t="inlineStr"/>
-      <c r="AD4" t="inlineStr"/>
+      <c r="AA4" t="n">
+        <v>468.61</v>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
@@ -846,47 +852,62 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8306</v>
+        <v>0.8128</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8408</v>
+        <v>0.8247</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7607</v>
+        <v>0.7407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6725</v>
+        <v>0.6863</v>
       </c>
       <c r="M5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N5" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O5" t="n">
-        <v>6</v>
+        <v>0.6667</v>
       </c>
       <c r="P5" t="n">
-        <v>3.11</v>
+        <v>1</v>
       </c>
       <c r="Q5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S5" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T5" t="n">
+        <v>1</v>
+      </c>
+      <c r="U5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V5" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W5" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X5" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y5" t="n">
+        <v>3.51</v>
+      </c>
+      <c r="Z5" t="n">
         <v>48064</v>
       </c>
-      <c r="R5" t="n">
-        <v>448.16</v>
-      </c>
-      <c r="S5" t="inlineStr"/>
-      <c r="T5" t="inlineStr"/>
-      <c r="U5" t="inlineStr"/>
-      <c r="V5" t="inlineStr"/>
-      <c r="W5" t="inlineStr"/>
-      <c r="X5" t="inlineStr"/>
-      <c r="Y5" t="inlineStr"/>
-      <c r="Z5" t="inlineStr"/>
-      <c r="AA5" t="inlineStr"/>
-      <c r="AB5" t="inlineStr"/>
-      <c r="AC5" t="inlineStr"/>
-      <c r="AD5" t="inlineStr"/>
+      <c r="AA5" t="n">
+        <v>450.34</v>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
@@ -920,47 +941,62 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.7993</v>
+        <v>0.8206</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8097</v>
+        <v>0.8391999999999999</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7316</v>
+        <v>0.7398</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6341</v>
+        <v>0.6571</v>
       </c>
       <c r="M6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N6" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O6" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="P6" t="n">
-        <v>2.87</v>
+        <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>119648</v>
+        <v>0.5</v>
       </c>
       <c r="R6" t="n">
-        <v>412.72</v>
-      </c>
-      <c r="S6" t="inlineStr"/>
-      <c r="T6" t="inlineStr"/>
-      <c r="U6" t="inlineStr"/>
-      <c r="V6" t="inlineStr"/>
-      <c r="W6" t="inlineStr"/>
-      <c r="X6" t="inlineStr"/>
-      <c r="Y6" t="inlineStr"/>
-      <c r="Z6" t="inlineStr"/>
-      <c r="AA6" t="inlineStr"/>
-      <c r="AB6" t="inlineStr"/>
-      <c r="AC6" t="inlineStr"/>
-      <c r="AD6" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S6" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T6" t="n">
+        <v>1</v>
+      </c>
+      <c r="U6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V6" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W6" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X6" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y6" t="n">
+        <v>1.32</v>
+      </c>
+      <c r="Z6" t="n">
+        <v>120704</v>
+      </c>
+      <c r="AA6" t="n">
+        <v>415.17</v>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="inlineStr">
@@ -994,47 +1030,62 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8806</v>
+        <v>0.8912</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8975</v>
+        <v>0.9077</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7632</v>
+        <v>0.7675</v>
       </c>
       <c r="L7" t="n">
-        <v>0.711</v>
+        <v>0.717</v>
       </c>
       <c r="M7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N7" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O7" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="P7" t="n">
-        <v>8.300000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S7" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T7" t="n">
+        <v>1</v>
+      </c>
+      <c r="U7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V7" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W7" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X7" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y7" t="n">
+        <v>7.16</v>
+      </c>
+      <c r="Z7" t="n">
         <v>957536</v>
       </c>
-      <c r="R7" t="n">
-        <v>483.75</v>
-      </c>
-      <c r="S7" t="inlineStr"/>
-      <c r="T7" t="inlineStr"/>
-      <c r="U7" t="inlineStr"/>
-      <c r="V7" t="inlineStr"/>
-      <c r="W7" t="inlineStr"/>
-      <c r="X7" t="inlineStr"/>
-      <c r="Y7" t="inlineStr"/>
-      <c r="Z7" t="inlineStr"/>
-      <c r="AA7" t="inlineStr"/>
-      <c r="AB7" t="inlineStr"/>
-      <c r="AC7" t="inlineStr"/>
-      <c r="AD7" t="inlineStr"/>
+      <c r="AA7" t="n">
+        <v>486.57</v>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="inlineStr">
@@ -1068,47 +1119,62 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7716</v>
+        <v>0.7995</v>
       </c>
       <c r="J8" t="n">
-        <v>0.768</v>
+        <v>0.803</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7173</v>
+        <v>0.738</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6352</v>
+        <v>0.6659</v>
       </c>
       <c r="M8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N8" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O8" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="P8" t="n">
-        <v>7.13</v>
+        <v>1</v>
       </c>
       <c r="Q8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S8" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T8" t="n">
+        <v>1</v>
+      </c>
+      <c r="U8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V8" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W8" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X8" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y8" t="n">
+        <v>2.56</v>
+      </c>
+      <c r="Z8" t="n">
         <v>239168</v>
       </c>
-      <c r="R8" t="n">
-        <v>621.73</v>
-      </c>
-      <c r="S8" t="inlineStr"/>
-      <c r="T8" t="inlineStr"/>
-      <c r="U8" t="inlineStr"/>
-      <c r="V8" t="inlineStr"/>
-      <c r="W8" t="inlineStr"/>
-      <c r="X8" t="inlineStr"/>
-      <c r="Y8" t="inlineStr"/>
-      <c r="Z8" t="inlineStr"/>
-      <c r="AA8" t="inlineStr"/>
-      <c r="AB8" t="inlineStr"/>
-      <c r="AC8" t="inlineStr"/>
-      <c r="AD8" t="inlineStr"/>
+      <c r="AA8" t="n">
+        <v>623.39</v>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="inlineStr">
@@ -1142,47 +1208,62 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7779</v>
+        <v>0.7983</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7665999999999999</v>
+        <v>0.8016</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7482</v>
+        <v>0.7467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6412</v>
+        <v>0.6538</v>
       </c>
       <c r="M9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N9" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O9" t="n">
-        <v>0</v>
+        <v>0.6667</v>
       </c>
       <c r="P9" t="n">
-        <v>6.84</v>
+        <v>1</v>
       </c>
       <c r="Q9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S9" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T9" t="n">
+        <v>1</v>
+      </c>
+      <c r="U9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V9" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W9" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X9" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y9" t="n">
+        <v>8.66</v>
+      </c>
+      <c r="Z9" t="n">
         <v>120704</v>
       </c>
-      <c r="R9" t="n">
-        <v>605.86</v>
-      </c>
-      <c r="S9" t="inlineStr"/>
-      <c r="T9" t="inlineStr"/>
-      <c r="U9" t="inlineStr"/>
-      <c r="V9" t="inlineStr"/>
-      <c r="W9" t="inlineStr"/>
-      <c r="X9" t="inlineStr"/>
-      <c r="Y9" t="inlineStr"/>
-      <c r="Z9" t="inlineStr"/>
-      <c r="AA9" t="inlineStr"/>
-      <c r="AB9" t="inlineStr"/>
-      <c r="AC9" t="inlineStr"/>
-      <c r="AD9" t="inlineStr"/>
+      <c r="AA9" t="n">
+        <v>612.4299999999999</v>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="inlineStr">
@@ -1216,47 +1297,62 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9162</v>
+        <v>0.769</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9291</v>
+        <v>0.8069</v>
       </c>
       <c r="K10" t="n">
-        <v>0.7879</v>
+        <v>0.6675</v>
       </c>
       <c r="L10" t="n">
-        <v>0.6961000000000001</v>
+        <v>0.9971</v>
       </c>
       <c r="M10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N10" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O10" t="n">
-        <v>12</v>
+        <v>0.6667</v>
       </c>
       <c r="P10" t="n">
-        <v>5.68</v>
+        <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>17152</v>
+        <v>0.5</v>
       </c>
       <c r="R10" t="n">
-        <v>482.62</v>
-      </c>
-      <c r="S10" t="inlineStr"/>
-      <c r="T10" t="inlineStr"/>
-      <c r="U10" t="inlineStr"/>
-      <c r="V10" t="inlineStr"/>
-      <c r="W10" t="inlineStr"/>
-      <c r="X10" t="inlineStr"/>
-      <c r="Y10" t="inlineStr"/>
-      <c r="Z10" t="inlineStr"/>
-      <c r="AA10" t="inlineStr"/>
-      <c r="AB10" t="inlineStr"/>
-      <c r="AC10" t="inlineStr"/>
-      <c r="AD10" t="inlineStr"/>
+        <v>0.5</v>
+      </c>
+      <c r="S10" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T10" t="n">
+        <v>1</v>
+      </c>
+      <c r="U10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V10" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W10" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X10" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y10" t="n">
+        <v>1.15</v>
+      </c>
+      <c r="Z10" t="n">
+        <v>18208</v>
+      </c>
+      <c r="AA10" t="n">
+        <v>497.71</v>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="inlineStr">
@@ -1290,47 +1386,62 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9286</v>
+        <v>0.9402</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9283</v>
+        <v>0.9353</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7941</v>
+        <v>0.8131</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7191</v>
+        <v>0.7015</v>
       </c>
       <c r="M11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N11" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O11" t="n">
-        <v>12</v>
+        <v>0.6667</v>
       </c>
       <c r="P11" t="n">
-        <v>26.59</v>
+        <v>1</v>
       </c>
       <c r="Q11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S11" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T11" t="n">
+        <v>1</v>
+      </c>
+      <c r="U11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V11" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W11" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X11" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y11" t="n">
+        <v>20.34</v>
+      </c>
+      <c r="Z11" t="n">
         <v>137568</v>
       </c>
-      <c r="R11" t="n">
-        <v>829.01</v>
-      </c>
-      <c r="S11" t="inlineStr"/>
-      <c r="T11" t="inlineStr"/>
-      <c r="U11" t="inlineStr"/>
-      <c r="V11" t="inlineStr"/>
-      <c r="W11" t="inlineStr"/>
-      <c r="X11" t="inlineStr"/>
-      <c r="Y11" t="inlineStr"/>
-      <c r="Z11" t="inlineStr"/>
-      <c r="AA11" t="inlineStr"/>
-      <c r="AB11" t="inlineStr"/>
-      <c r="AC11" t="inlineStr"/>
-      <c r="AD11" t="inlineStr"/>
+      <c r="AA11" t="n">
+        <v>849.0700000000001</v>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="inlineStr">
@@ -1364,47 +1475,62 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8182</v>
+        <v>0.8656</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8234</v>
+        <v>0.8773</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7389</v>
+        <v>0.7624</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6441</v>
+        <v>0.6726</v>
       </c>
       <c r="M12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N12" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O12" t="n">
-        <v>12</v>
+        <v>0.6667</v>
       </c>
       <c r="P12" t="n">
-        <v>8.93</v>
+        <v>1</v>
       </c>
       <c r="Q12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S12" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T12" t="n">
+        <v>1</v>
+      </c>
+      <c r="U12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V12" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W12" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X12" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y12" t="n">
+        <v>5.36</v>
+      </c>
+      <c r="Z12" t="n">
         <v>34176</v>
       </c>
-      <c r="R12" t="n">
-        <v>646.27</v>
-      </c>
-      <c r="S12" t="inlineStr"/>
-      <c r="T12" t="inlineStr"/>
-      <c r="U12" t="inlineStr"/>
-      <c r="V12" t="inlineStr"/>
-      <c r="W12" t="inlineStr"/>
-      <c r="X12" t="inlineStr"/>
-      <c r="Y12" t="inlineStr"/>
-      <c r="Z12" t="inlineStr"/>
-      <c r="AA12" t="inlineStr"/>
-      <c r="AB12" t="inlineStr"/>
-      <c r="AC12" t="inlineStr"/>
-      <c r="AD12" t="inlineStr"/>
+      <c r="AA12" t="n">
+        <v>664.39</v>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="inlineStr">
@@ -1438,47 +1564,62 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.8759</v>
+        <v>0.7292999999999999</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8986</v>
+        <v>0.7558</v>
       </c>
       <c r="K13" t="n">
-        <v>0.7607</v>
+        <v>0.6501</v>
       </c>
       <c r="L13" t="n">
-        <v>0.6832</v>
+        <v>0.93</v>
       </c>
       <c r="M13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="N13" t="n">
-        <v>0</v>
+        <v>0.5</v>
       </c>
       <c r="O13" t="n">
-        <v>12</v>
+        <v>0.6667</v>
       </c>
       <c r="P13" t="n">
-        <v>8.800000000000001</v>
+        <v>1</v>
       </c>
       <c r="Q13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="R13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S13" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="T13" t="n">
+        <v>1</v>
+      </c>
+      <c r="U13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V13" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="W13" t="n">
+        <v>0.6667</v>
+      </c>
+      <c r="X13" t="n">
+        <v>1</v>
+      </c>
+      <c r="Y13" t="n">
+        <v>1.84</v>
+      </c>
+      <c r="Z13" t="n">
         <v>18208</v>
       </c>
-      <c r="R13" t="n">
-        <v>601.8099999999999</v>
-      </c>
-      <c r="S13" t="inlineStr"/>
-      <c r="T13" t="inlineStr"/>
-      <c r="U13" t="inlineStr"/>
-      <c r="V13" t="inlineStr"/>
-      <c r="W13" t="inlineStr"/>
-      <c r="X13" t="inlineStr"/>
-      <c r="Y13" t="inlineStr"/>
-      <c r="Z13" t="inlineStr"/>
-      <c r="AA13" t="inlineStr"/>
-      <c r="AB13" t="inlineStr"/>
-      <c r="AC13" t="inlineStr"/>
-      <c r="AD13" t="inlineStr"/>
+      <c r="AA13" t="n">
+        <v>614.4299999999999</v>
+      </c>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,22 +585,22 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7886</v>
+        <v>0.7952</v>
       </c>
       <c r="J2" t="n">
-        <v>0.8027</v>
+        <v>0.805</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7204</v>
+        <v>0.7295</v>
       </c>
       <c r="L2" t="n">
-        <v>0.6711</v>
+        <v>0.9</v>
       </c>
       <c r="M2" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="N2" t="n">
-        <v>0.5</v>
+        <v>0.6551</v>
       </c>
       <c r="O2" t="n">
         <v>0.6667</v>
@@ -609,10 +609,10 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="R2" t="n">
-        <v>0.5</v>
+        <v>0.6558</v>
       </c>
       <c r="S2" t="n">
         <v>0.6667</v>
@@ -621,25 +621,25 @@
         <v>1</v>
       </c>
       <c r="U2" t="n">
-        <v>0.5</v>
+        <v>0.6256</v>
       </c>
       <c r="V2" t="n">
-        <v>0.5</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W2" t="n">
-        <v>0.6667</v>
+        <v>0.6083</v>
       </c>
       <c r="X2" t="n">
-        <v>1</v>
+        <v>0.5019</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.93</v>
+        <v>0.6</v>
       </c>
       <c r="Z2" t="n">
         <v>48064</v>
       </c>
       <c r="AA2" t="n">
-        <v>384.54</v>
+        <v>385.45</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,13 +585,13 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7952</v>
+        <v>0.7953</v>
       </c>
       <c r="J2" t="n">
         <v>0.805</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7295</v>
+        <v>0.7298</v>
       </c>
       <c r="L2" t="n">
         <v>0.9</v>
@@ -633,13 +633,13 @@
         <v>0.5019</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.6</v>
+        <v>0.91</v>
       </c>
       <c r="Z2" t="n">
         <v>48064</v>
       </c>
       <c r="AA2" t="n">
-        <v>385.45</v>
+        <v>385.02</v>
       </c>
     </row>
     <row r="3">
@@ -680,16 +680,16 @@
         <v>0.8917</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7736</v>
+        <v>0.7739</v>
       </c>
       <c r="L3" t="n">
-        <v>0.7227</v>
+        <v>1</v>
       </c>
       <c r="M3" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="N3" t="n">
-        <v>0.5</v>
+        <v>0.6551</v>
       </c>
       <c r="O3" t="n">
         <v>0.6667</v>
@@ -698,10 +698,10 @@
         <v>1</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="R3" t="n">
-        <v>0.5</v>
+        <v>0.6558</v>
       </c>
       <c r="S3" t="n">
         <v>0.6667</v>
@@ -710,25 +710,25 @@
         <v>1</v>
       </c>
       <c r="U3" t="n">
-        <v>0.5</v>
+        <v>0.6256</v>
       </c>
       <c r="V3" t="n">
-        <v>0.5</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W3" t="n">
-        <v>0.6667</v>
+        <v>0.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>1</v>
+        <v>0.5019</v>
       </c>
       <c r="Y3" t="n">
-        <v>2.66</v>
+        <v>3.84</v>
       </c>
       <c r="Z3" t="n">
         <v>376416</v>
       </c>
       <c r="AA3" t="n">
-        <v>470.86</v>
+        <v>470.24</v>
       </c>
     </row>
     <row r="4">
@@ -772,13 +772,13 @@
         <v>0.7388</v>
       </c>
       <c r="L4" t="n">
-        <v>0.6649</v>
+        <v>0.9</v>
       </c>
       <c r="M4" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="N4" t="n">
-        <v>0.5</v>
+        <v>0.6551</v>
       </c>
       <c r="O4" t="n">
         <v>0.6667</v>
@@ -787,10 +787,10 @@
         <v>1</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="R4" t="n">
-        <v>0.5</v>
+        <v>0.6558</v>
       </c>
       <c r="S4" t="n">
         <v>0.6667</v>
@@ -799,25 +799,25 @@
         <v>1</v>
       </c>
       <c r="U4" t="n">
-        <v>0.5</v>
+        <v>0.6256</v>
       </c>
       <c r="V4" t="n">
-        <v>0.5</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W4" t="n">
-        <v>0.6667</v>
+        <v>0.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>1</v>
+        <v>0.5019</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.65</v>
+        <v>2.22</v>
       </c>
       <c r="Z4" t="n">
         <v>93888</v>
       </c>
       <c r="AA4" t="n">
-        <v>468.61</v>
+        <v>466.99</v>
       </c>
     </row>
     <row r="5">
@@ -861,13 +861,13 @@
         <v>0.7407</v>
       </c>
       <c r="L5" t="n">
-        <v>0.6863</v>
+        <v>1</v>
       </c>
       <c r="M5" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="N5" t="n">
-        <v>0.5</v>
+        <v>0.6551</v>
       </c>
       <c r="O5" t="n">
         <v>0.6667</v>
@@ -876,10 +876,10 @@
         <v>1</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.5</v>
+        <v>0.6561</v>
       </c>
       <c r="R5" t="n">
-        <v>0.5</v>
+        <v>0.6558</v>
       </c>
       <c r="S5" t="n">
         <v>0.6667</v>
@@ -888,25 +888,25 @@
         <v>1</v>
       </c>
       <c r="U5" t="n">
-        <v>0.5</v>
+        <v>0.6256</v>
       </c>
       <c r="V5" t="n">
-        <v>0.5</v>
+        <v>0.6749000000000001</v>
       </c>
       <c r="W5" t="n">
-        <v>0.6667</v>
+        <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>1</v>
+        <v>0.5019</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.51</v>
+        <v>4.81</v>
       </c>
       <c r="Z5" t="n">
         <v>48064</v>
       </c>
       <c r="AA5" t="n">
-        <v>450.34</v>
+        <v>450.72</v>
       </c>
     </row>
     <row r="6">
@@ -941,22 +941,22 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8206</v>
+        <v>0.8021</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8391999999999999</v>
+        <v>0.819</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7398</v>
+        <v>0.7399</v>
       </c>
       <c r="L6" t="n">
-        <v>0.6571</v>
+        <v>1</v>
       </c>
       <c r="M6" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="N6" t="n">
-        <v>0.5</v>
+        <v>0.6212</v>
       </c>
       <c r="O6" t="n">
         <v>0.6667</v>
@@ -965,10 +965,10 @@
         <v>1</v>
       </c>
       <c r="Q6" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="R6" t="n">
-        <v>0.5</v>
+        <v>0.6216</v>
       </c>
       <c r="S6" t="n">
         <v>0.6667</v>
@@ -977,25 +977,25 @@
         <v>1</v>
       </c>
       <c r="U6" t="n">
-        <v>0.5</v>
+        <v>0.586</v>
       </c>
       <c r="V6" t="n">
-        <v>0.5</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="W6" t="n">
-        <v>0.6667</v>
+        <v>0.5584</v>
       </c>
       <c r="X6" t="n">
-        <v>1</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.32</v>
+        <v>1.12</v>
       </c>
       <c r="Z6" t="n">
         <v>120704</v>
       </c>
       <c r="AA6" t="n">
-        <v>415.17</v>
+        <v>415.03</v>
       </c>
     </row>
     <row r="7">
@@ -1030,22 +1030,22 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8912</v>
+        <v>0.8904</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9077</v>
+        <v>0.9073</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7675</v>
+        <v>0.7681</v>
       </c>
       <c r="L7" t="n">
-        <v>0.717</v>
+        <v>1</v>
       </c>
       <c r="M7" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="N7" t="n">
-        <v>0.5</v>
+        <v>0.6212</v>
       </c>
       <c r="O7" t="n">
         <v>0.6667</v>
@@ -1054,10 +1054,10 @@
         <v>1</v>
       </c>
       <c r="Q7" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="R7" t="n">
-        <v>0.5</v>
+        <v>0.6216</v>
       </c>
       <c r="S7" t="n">
         <v>0.6667</v>
@@ -1066,25 +1066,25 @@
         <v>1</v>
       </c>
       <c r="U7" t="n">
-        <v>0.5</v>
+        <v>0.586</v>
       </c>
       <c r="V7" t="n">
-        <v>0.5</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="W7" t="n">
-        <v>0.6667</v>
+        <v>0.5584</v>
       </c>
       <c r="X7" t="n">
-        <v>1</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>7.16</v>
+        <v>11.07</v>
       </c>
       <c r="Z7" t="n">
         <v>957536</v>
       </c>
       <c r="AA7" t="n">
-        <v>486.57</v>
+        <v>486.24</v>
       </c>
     </row>
     <row r="8">
@@ -1119,22 +1119,22 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7995</v>
+        <v>0.8004</v>
       </c>
       <c r="J8" t="n">
-        <v>0.803</v>
+        <v>0.8033</v>
       </c>
       <c r="K8" t="n">
-        <v>0.738</v>
+        <v>0.7403999999999999</v>
       </c>
       <c r="L8" t="n">
-        <v>0.6659</v>
+        <v>1</v>
       </c>
       <c r="M8" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="N8" t="n">
-        <v>0.5</v>
+        <v>0.6212</v>
       </c>
       <c r="O8" t="n">
         <v>0.6667</v>
@@ -1143,10 +1143,10 @@
         <v>1</v>
       </c>
       <c r="Q8" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="R8" t="n">
-        <v>0.5</v>
+        <v>0.6216</v>
       </c>
       <c r="S8" t="n">
         <v>0.6667</v>
@@ -1155,25 +1155,25 @@
         <v>1</v>
       </c>
       <c r="U8" t="n">
-        <v>0.5</v>
+        <v>0.586</v>
       </c>
       <c r="V8" t="n">
-        <v>0.5</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="W8" t="n">
-        <v>0.6667</v>
+        <v>0.5584</v>
       </c>
       <c r="X8" t="n">
-        <v>1</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>2.56</v>
+        <v>3.26</v>
       </c>
       <c r="Z8" t="n">
         <v>239168</v>
       </c>
       <c r="AA8" t="n">
-        <v>623.39</v>
+        <v>627.21</v>
       </c>
     </row>
     <row r="9">
@@ -1217,13 +1217,13 @@
         <v>0.7467</v>
       </c>
       <c r="L9" t="n">
-        <v>0.6538</v>
+        <v>1</v>
       </c>
       <c r="M9" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="N9" t="n">
-        <v>0.5</v>
+        <v>0.6212</v>
       </c>
       <c r="O9" t="n">
         <v>0.6667</v>
@@ -1232,10 +1232,10 @@
         <v>1</v>
       </c>
       <c r="Q9" t="n">
-        <v>0.5</v>
+        <v>0.6227</v>
       </c>
       <c r="R9" t="n">
-        <v>0.5</v>
+        <v>0.6216</v>
       </c>
       <c r="S9" t="n">
         <v>0.6667</v>
@@ -1244,25 +1244,25 @@
         <v>1</v>
       </c>
       <c r="U9" t="n">
-        <v>0.5</v>
+        <v>0.586</v>
       </c>
       <c r="V9" t="n">
-        <v>0.5</v>
+        <v>0.6588000000000001</v>
       </c>
       <c r="W9" t="n">
-        <v>0.6667</v>
+        <v>0.5584</v>
       </c>
       <c r="X9" t="n">
-        <v>1</v>
+        <v>0.5489000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>8.66</v>
+        <v>9.48</v>
       </c>
       <c r="Z9" t="n">
         <v>120704</v>
       </c>
       <c r="AA9" t="n">
-        <v>612.4299999999999</v>
+        <v>612.72</v>
       </c>
     </row>
     <row r="10">
@@ -1297,22 +1297,22 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.769</v>
+        <v>0.5253</v>
       </c>
       <c r="J10" t="n">
-        <v>0.8069</v>
+        <v>0.5877</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6675</v>
+        <v>0.6666</v>
       </c>
       <c r="L10" t="n">
-        <v>0.9971</v>
+        <v>1</v>
       </c>
       <c r="M10" t="n">
-        <v>0.5</v>
+        <v>0.619</v>
       </c>
       <c r="N10" t="n">
-        <v>0.5</v>
+        <v>0.6188</v>
       </c>
       <c r="O10" t="n">
         <v>0.6667</v>
@@ -1321,10 +1321,10 @@
         <v>1</v>
       </c>
       <c r="Q10" t="n">
-        <v>0.5</v>
+        <v>0.6191</v>
       </c>
       <c r="R10" t="n">
-        <v>0.5</v>
+        <v>0.6193</v>
       </c>
       <c r="S10" t="n">
         <v>0.6667</v>
@@ -1333,16 +1333,16 @@
         <v>1</v>
       </c>
       <c r="U10" t="n">
-        <v>0.5</v>
+        <v>0.7202</v>
       </c>
       <c r="V10" t="n">
-        <v>0.5</v>
+        <v>0.7835</v>
       </c>
       <c r="W10" t="n">
-        <v>0.6667</v>
+        <v>0.7042</v>
       </c>
       <c r="X10" t="n">
-        <v>1</v>
+        <v>0.5028</v>
       </c>
       <c r="Y10" t="n">
         <v>1.15</v>
@@ -1351,7 +1351,7 @@
         <v>18208</v>
       </c>
       <c r="AA10" t="n">
-        <v>497.71</v>
+        <v>494.07</v>
       </c>
     </row>
     <row r="11">
@@ -1395,13 +1395,13 @@
         <v>0.8131</v>
       </c>
       <c r="L11" t="n">
-        <v>0.7015</v>
+        <v>0.9</v>
       </c>
       <c r="M11" t="n">
-        <v>0.5</v>
+        <v>0.619</v>
       </c>
       <c r="N11" t="n">
-        <v>0.5</v>
+        <v>0.6188</v>
       </c>
       <c r="O11" t="n">
         <v>0.6667</v>
@@ -1410,10 +1410,10 @@
         <v>1</v>
       </c>
       <c r="Q11" t="n">
-        <v>0.5</v>
+        <v>0.6191</v>
       </c>
       <c r="R11" t="n">
-        <v>0.5</v>
+        <v>0.6193</v>
       </c>
       <c r="S11" t="n">
         <v>0.6667</v>
@@ -1422,25 +1422,25 @@
         <v>1</v>
       </c>
       <c r="U11" t="n">
-        <v>0.5</v>
+        <v>0.7202</v>
       </c>
       <c r="V11" t="n">
-        <v>0.5</v>
+        <v>0.7835</v>
       </c>
       <c r="W11" t="n">
-        <v>0.6667</v>
+        <v>0.7042</v>
       </c>
       <c r="X11" t="n">
-        <v>1</v>
+        <v>0.5028</v>
       </c>
       <c r="Y11" t="n">
-        <v>20.34</v>
+        <v>20.64</v>
       </c>
       <c r="Z11" t="n">
         <v>137568</v>
       </c>
       <c r="AA11" t="n">
-        <v>849.0700000000001</v>
+        <v>848.09</v>
       </c>
     </row>
     <row r="12">
@@ -1481,16 +1481,16 @@
         <v>0.8773</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7624</v>
+        <v>0.7622</v>
       </c>
       <c r="L12" t="n">
-        <v>0.6726</v>
+        <v>1</v>
       </c>
       <c r="M12" t="n">
-        <v>0.5</v>
+        <v>0.619</v>
       </c>
       <c r="N12" t="n">
-        <v>0.5</v>
+        <v>0.6188</v>
       </c>
       <c r="O12" t="n">
         <v>0.6667</v>
@@ -1499,10 +1499,10 @@
         <v>1</v>
       </c>
       <c r="Q12" t="n">
-        <v>0.5</v>
+        <v>0.6191</v>
       </c>
       <c r="R12" t="n">
-        <v>0.5</v>
+        <v>0.6193</v>
       </c>
       <c r="S12" t="n">
         <v>0.6667</v>
@@ -1511,25 +1511,25 @@
         <v>1</v>
       </c>
       <c r="U12" t="n">
-        <v>0.5</v>
+        <v>0.7202</v>
       </c>
       <c r="V12" t="n">
-        <v>0.5</v>
+        <v>0.7835</v>
       </c>
       <c r="W12" t="n">
-        <v>0.6667</v>
+        <v>0.7042</v>
       </c>
       <c r="X12" t="n">
-        <v>1</v>
+        <v>0.5028</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.36</v>
+        <v>5.5</v>
       </c>
       <c r="Z12" t="n">
         <v>34176</v>
       </c>
       <c r="AA12" t="n">
-        <v>664.39</v>
+        <v>664.5</v>
       </c>
     </row>
     <row r="13">
@@ -1564,22 +1564,22 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7292999999999999</v>
+        <v>0.7297</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7558</v>
+        <v>0.7559</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6501</v>
+        <v>0.6508</v>
       </c>
       <c r="L13" t="n">
-        <v>0.93</v>
+        <v>1</v>
       </c>
       <c r="M13" t="n">
-        <v>0.5</v>
+        <v>0.619</v>
       </c>
       <c r="N13" t="n">
-        <v>0.5</v>
+        <v>0.6188</v>
       </c>
       <c r="O13" t="n">
         <v>0.6667</v>
@@ -1588,10 +1588,10 @@
         <v>1</v>
       </c>
       <c r="Q13" t="n">
-        <v>0.5</v>
+        <v>0.6191</v>
       </c>
       <c r="R13" t="n">
-        <v>0.5</v>
+        <v>0.6193</v>
       </c>
       <c r="S13" t="n">
         <v>0.6667</v>
@@ -1600,25 +1600,25 @@
         <v>1</v>
       </c>
       <c r="U13" t="n">
-        <v>0.5</v>
+        <v>0.7202</v>
       </c>
       <c r="V13" t="n">
-        <v>0.5</v>
+        <v>0.7835</v>
       </c>
       <c r="W13" t="n">
-        <v>0.6667</v>
+        <v>0.7042</v>
       </c>
       <c r="X13" t="n">
-        <v>1</v>
+        <v>0.5028</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.84</v>
+        <v>1.87</v>
       </c>
       <c r="Z13" t="n">
         <v>18208</v>
       </c>
       <c r="AA13" t="n">
-        <v>614.4299999999999</v>
+        <v>615.23</v>
       </c>
     </row>
   </sheetData>

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -591,7 +591,7 @@
         <v>0.805</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7298</v>
+        <v>0.7295</v>
       </c>
       <c r="L2" t="n">
         <v>0.9</v>
@@ -633,13 +633,13 @@
         <v>0.5019</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.91</v>
+        <v>0.64</v>
       </c>
       <c r="Z2" t="n">
         <v>48064</v>
       </c>
       <c r="AA2" t="n">
-        <v>385.02</v>
+        <v>384.55</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,13 +585,13 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7953</v>
+        <v>0.7852</v>
       </c>
       <c r="J2" t="n">
-        <v>0.805</v>
+        <v>0.7867</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7295</v>
+        <v>0.733</v>
       </c>
       <c r="L2" t="n">
         <v>0.9</v>
@@ -609,10 +609,10 @@
         <v>1</v>
       </c>
       <c r="Q2" t="n">
-        <v>0.6561</v>
+        <v>0.6562</v>
       </c>
       <c r="R2" t="n">
-        <v>0.6558</v>
+        <v>0.6559</v>
       </c>
       <c r="S2" t="n">
         <v>0.6667</v>
@@ -633,13 +633,13 @@
         <v>0.5019</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.64</v>
+        <v>0.88</v>
       </c>
       <c r="Z2" t="n">
-        <v>48064</v>
+        <v>48128</v>
       </c>
       <c r="AA2" t="n">
-        <v>384.55</v>
+        <v>386.03</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,10 +585,10 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7852</v>
+        <v>0.7851</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7867</v>
+        <v>0.7866</v>
       </c>
       <c r="K2" t="n">
         <v>0.733</v>
@@ -606,7 +606,7 @@
         <v>0.6667</v>
       </c>
       <c r="P2" t="n">
-        <v>1</v>
+        <v>0.9953</v>
       </c>
       <c r="Q2" t="n">
         <v>0.6562</v>
@@ -618,7 +618,7 @@
         <v>0.6667</v>
       </c>
       <c r="T2" t="n">
-        <v>1</v>
+        <v>0.9905</v>
       </c>
       <c r="U2" t="n">
         <v>0.6256</v>
@@ -630,16 +630,16 @@
         <v>0.6083</v>
       </c>
       <c r="X2" t="n">
-        <v>0.5019</v>
+        <v>0.891</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.88</v>
+        <v>1.45</v>
       </c>
       <c r="Z2" t="n">
         <v>48128</v>
       </c>
       <c r="AA2" t="n">
-        <v>386.03</v>
+        <v>397.07</v>
       </c>
     </row>
     <row r="3">
@@ -674,16 +674,16 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.8866000000000001</v>
+        <v>0.7657</v>
       </c>
       <c r="J3" t="n">
-        <v>0.8917</v>
+        <v>0.7496</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7739</v>
+        <v>0.7185</v>
       </c>
       <c r="L3" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M3" t="n">
         <v>0.6561</v>
@@ -695,19 +695,19 @@
         <v>0.6667</v>
       </c>
       <c r="P3" t="n">
-        <v>1</v>
+        <v>0.9953</v>
       </c>
       <c r="Q3" t="n">
-        <v>0.6561</v>
+        <v>0.6562</v>
       </c>
       <c r="R3" t="n">
-        <v>0.6558</v>
+        <v>0.6559</v>
       </c>
       <c r="S3" t="n">
         <v>0.6667</v>
       </c>
       <c r="T3" t="n">
-        <v>1</v>
+        <v>0.9905</v>
       </c>
       <c r="U3" t="n">
         <v>0.6256</v>
@@ -719,16 +719,16 @@
         <v>0.6083</v>
       </c>
       <c r="X3" t="n">
-        <v>0.5019</v>
+        <v>0.891</v>
       </c>
       <c r="Y3" t="n">
-        <v>3.84</v>
+        <v>1.95</v>
       </c>
       <c r="Z3" t="n">
-        <v>376416</v>
+        <v>48256</v>
       </c>
       <c r="AA3" t="n">
-        <v>470.24</v>
+        <v>405.71</v>
       </c>
     </row>
     <row r="4">
@@ -763,16 +763,16 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7875</v>
+        <v>0.7931</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7818000000000001</v>
+        <v>0.7788</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7388</v>
+        <v>0.7519</v>
       </c>
       <c r="L4" t="n">
-        <v>0.9</v>
+        <v>1</v>
       </c>
       <c r="M4" t="n">
         <v>0.6561</v>
@@ -784,19 +784,19 @@
         <v>0.6667</v>
       </c>
       <c r="P4" t="n">
-        <v>1</v>
+        <v>0.9953</v>
       </c>
       <c r="Q4" t="n">
-        <v>0.6561</v>
+        <v>0.6562</v>
       </c>
       <c r="R4" t="n">
-        <v>0.6558</v>
+        <v>0.6559</v>
       </c>
       <c r="S4" t="n">
         <v>0.6667</v>
       </c>
       <c r="T4" t="n">
-        <v>1</v>
+        <v>0.9905</v>
       </c>
       <c r="U4" t="n">
         <v>0.6256</v>
@@ -808,16 +808,16 @@
         <v>0.6083</v>
       </c>
       <c r="X4" t="n">
-        <v>0.5019</v>
+        <v>0.891</v>
       </c>
       <c r="Y4" t="n">
-        <v>2.22</v>
+        <v>1.79</v>
       </c>
       <c r="Z4" t="n">
-        <v>93888</v>
+        <v>95008</v>
       </c>
       <c r="AA4" t="n">
-        <v>466.99</v>
+        <v>481.73</v>
       </c>
     </row>
     <row r="5">
@@ -852,13 +852,13 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.8128</v>
+        <v>0.7814</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8247</v>
+        <v>0.8025</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7407</v>
+        <v>0.7226</v>
       </c>
       <c r="L5" t="n">
         <v>1</v>
@@ -873,19 +873,19 @@
         <v>0.6667</v>
       </c>
       <c r="P5" t="n">
-        <v>1</v>
+        <v>0.9953</v>
       </c>
       <c r="Q5" t="n">
-        <v>0.6561</v>
+        <v>0.6562</v>
       </c>
       <c r="R5" t="n">
-        <v>0.6558</v>
+        <v>0.6559</v>
       </c>
       <c r="S5" t="n">
         <v>0.6667</v>
       </c>
       <c r="T5" t="n">
-        <v>1</v>
+        <v>0.9905</v>
       </c>
       <c r="U5" t="n">
         <v>0.6256</v>
@@ -897,16 +897,16 @@
         <v>0.6083</v>
       </c>
       <c r="X5" t="n">
-        <v>0.5019</v>
+        <v>0.891</v>
       </c>
       <c r="Y5" t="n">
-        <v>4.81</v>
+        <v>3.08</v>
       </c>
       <c r="Z5" t="n">
-        <v>48064</v>
+        <v>49184</v>
       </c>
       <c r="AA5" t="n">
-        <v>450.72</v>
+        <v>464.91</v>
       </c>
     </row>
     <row r="6">
@@ -941,13 +941,13 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.8021</v>
+        <v>0.802</v>
       </c>
       <c r="J6" t="n">
-        <v>0.819</v>
+        <v>0.8135</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7399</v>
+        <v>0.7423999999999999</v>
       </c>
       <c r="L6" t="n">
         <v>1</v>
@@ -962,19 +962,19 @@
         <v>0.6667</v>
       </c>
       <c r="P6" t="n">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="Q6" t="n">
         <v>0.6227</v>
       </c>
       <c r="R6" t="n">
-        <v>0.6216</v>
+        <v>0.622</v>
       </c>
       <c r="S6" t="n">
         <v>0.6667</v>
       </c>
       <c r="T6" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="U6" t="n">
         <v>0.586</v>
@@ -986,16 +986,16 @@
         <v>0.5584</v>
       </c>
       <c r="X6" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>1.12</v>
+        <v>0.91</v>
       </c>
       <c r="Z6" t="n">
-        <v>120704</v>
+        <v>120768</v>
       </c>
       <c r="AA6" t="n">
-        <v>415.03</v>
+        <v>429.31</v>
       </c>
     </row>
     <row r="7">
@@ -1030,13 +1030,13 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.8904</v>
+        <v>0.7849</v>
       </c>
       <c r="J7" t="n">
-        <v>0.9073</v>
+        <v>0.8048</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7681</v>
+        <v>0.7184</v>
       </c>
       <c r="L7" t="n">
         <v>1</v>
@@ -1051,19 +1051,19 @@
         <v>0.6667</v>
       </c>
       <c r="P7" t="n">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="Q7" t="n">
         <v>0.6227</v>
       </c>
       <c r="R7" t="n">
-        <v>0.6216</v>
+        <v>0.622</v>
       </c>
       <c r="S7" t="n">
         <v>0.6667</v>
       </c>
       <c r="T7" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="U7" t="n">
         <v>0.586</v>
@@ -1075,16 +1075,16 @@
         <v>0.5584</v>
       </c>
       <c r="X7" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>11.07</v>
+        <v>1.05</v>
       </c>
       <c r="Z7" t="n">
-        <v>957536</v>
+        <v>120896</v>
       </c>
       <c r="AA7" t="n">
-        <v>486.24</v>
+        <v>436.04</v>
       </c>
     </row>
     <row r="8">
@@ -1119,13 +1119,13 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.8004</v>
+        <v>0.7574</v>
       </c>
       <c r="J8" t="n">
-        <v>0.8033</v>
+        <v>0.7369</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7403999999999999</v>
+        <v>0.7203000000000001</v>
       </c>
       <c r="L8" t="n">
         <v>1</v>
@@ -1140,19 +1140,19 @@
         <v>0.6667</v>
       </c>
       <c r="P8" t="n">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="Q8" t="n">
         <v>0.6227</v>
       </c>
       <c r="R8" t="n">
-        <v>0.6216</v>
+        <v>0.622</v>
       </c>
       <c r="S8" t="n">
         <v>0.6667</v>
       </c>
       <c r="T8" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="U8" t="n">
         <v>0.586</v>
@@ -1164,16 +1164,16 @@
         <v>0.5584</v>
       </c>
       <c r="X8" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>3.26</v>
+        <v>4.43</v>
       </c>
       <c r="Z8" t="n">
-        <v>239168</v>
+        <v>240288</v>
       </c>
       <c r="AA8" t="n">
-        <v>627.21</v>
+        <v>634.96</v>
       </c>
     </row>
     <row r="9">
@@ -1208,13 +1208,13 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.7983</v>
+        <v>0.716</v>
       </c>
       <c r="J9" t="n">
-        <v>0.8016</v>
+        <v>0.7149</v>
       </c>
       <c r="K9" t="n">
-        <v>0.7467</v>
+        <v>0.702</v>
       </c>
       <c r="L9" t="n">
         <v>1</v>
@@ -1229,19 +1229,19 @@
         <v>0.6667</v>
       </c>
       <c r="P9" t="n">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="Q9" t="n">
         <v>0.6227</v>
       </c>
       <c r="R9" t="n">
-        <v>0.6216</v>
+        <v>0.622</v>
       </c>
       <c r="S9" t="n">
         <v>0.6667</v>
       </c>
       <c r="T9" t="n">
-        <v>1</v>
+        <v>0.989</v>
       </c>
       <c r="U9" t="n">
         <v>0.586</v>
@@ -1253,16 +1253,16 @@
         <v>0.5584</v>
       </c>
       <c r="X9" t="n">
-        <v>0.5489000000000001</v>
+        <v>0.8846000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>9.48</v>
+        <v>4.06</v>
       </c>
       <c r="Z9" t="n">
-        <v>120704</v>
+        <v>121824</v>
       </c>
       <c r="AA9" t="n">
-        <v>612.72</v>
+        <v>622.8</v>
       </c>
     </row>
     <row r="10">
@@ -1297,13 +1297,13 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.5253</v>
+        <v>0.9287</v>
       </c>
       <c r="J10" t="n">
-        <v>0.5877</v>
+        <v>0.9351</v>
       </c>
       <c r="K10" t="n">
-        <v>0.6666</v>
+        <v>0.802</v>
       </c>
       <c r="L10" t="n">
         <v>1</v>
@@ -1318,7 +1318,7 @@
         <v>0.6667</v>
       </c>
       <c r="P10" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="Q10" t="n">
         <v>0.6191</v>
@@ -1330,7 +1330,7 @@
         <v>0.6667</v>
       </c>
       <c r="T10" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="U10" t="n">
         <v>0.7202</v>
@@ -1342,16 +1342,16 @@
         <v>0.7042</v>
       </c>
       <c r="X10" t="n">
-        <v>0.5028</v>
+        <v>0.9549</v>
       </c>
       <c r="Y10" t="n">
-        <v>1.15</v>
+        <v>3.74</v>
       </c>
       <c r="Z10" t="n">
-        <v>18208</v>
+        <v>18272</v>
       </c>
       <c r="AA10" t="n">
-        <v>494.07</v>
+        <v>516.29</v>
       </c>
     </row>
     <row r="11">
@@ -1386,13 +1386,13 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.9402</v>
+        <v>0.8826000000000001</v>
       </c>
       <c r="J11" t="n">
-        <v>0.9353</v>
+        <v>0.8771</v>
       </c>
       <c r="K11" t="n">
-        <v>0.8131</v>
+        <v>0.7786999999999999</v>
       </c>
       <c r="L11" t="n">
         <v>0.9</v>
@@ -1407,7 +1407,7 @@
         <v>0.6667</v>
       </c>
       <c r="P11" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="Q11" t="n">
         <v>0.6191</v>
@@ -1419,7 +1419,7 @@
         <v>0.6667</v>
       </c>
       <c r="T11" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="U11" t="n">
         <v>0.7202</v>
@@ -1431,16 +1431,16 @@
         <v>0.7042</v>
       </c>
       <c r="X11" t="n">
-        <v>0.5028</v>
+        <v>0.9549</v>
       </c>
       <c r="Y11" t="n">
-        <v>20.64</v>
+        <v>8.550000000000001</v>
       </c>
       <c r="Z11" t="n">
-        <v>137568</v>
+        <v>18400</v>
       </c>
       <c r="AA11" t="n">
-        <v>848.09</v>
+        <v>572.59</v>
       </c>
     </row>
     <row r="12">
@@ -1475,16 +1475,16 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8656</v>
+        <v>0.8569</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8773</v>
+        <v>0.8622</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7622</v>
+        <v>0.7664</v>
       </c>
       <c r="L12" t="n">
-        <v>1</v>
+        <v>0.9</v>
       </c>
       <c r="M12" t="n">
         <v>0.619</v>
@@ -1496,7 +1496,7 @@
         <v>0.6667</v>
       </c>
       <c r="P12" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="Q12" t="n">
         <v>0.6191</v>
@@ -1508,7 +1508,7 @@
         <v>0.6667</v>
       </c>
       <c r="T12" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="U12" t="n">
         <v>0.7202</v>
@@ -1520,16 +1520,16 @@
         <v>0.7042</v>
       </c>
       <c r="X12" t="n">
-        <v>0.5028</v>
+        <v>0.9549</v>
       </c>
       <c r="Y12" t="n">
-        <v>5.5</v>
+        <v>7.19</v>
       </c>
       <c r="Z12" t="n">
-        <v>34176</v>
+        <v>35296</v>
       </c>
       <c r="AA12" t="n">
-        <v>664.5</v>
+        <v>688.35</v>
       </c>
     </row>
     <row r="13">
@@ -1564,13 +1564,13 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7297</v>
+        <v>0.7462</v>
       </c>
       <c r="J13" t="n">
-        <v>0.7559</v>
+        <v>0.8159</v>
       </c>
       <c r="K13" t="n">
-        <v>0.6508</v>
+        <v>0.662</v>
       </c>
       <c r="L13" t="n">
         <v>1</v>
@@ -1585,7 +1585,7 @@
         <v>0.6667</v>
       </c>
       <c r="P13" t="n">
-        <v>1</v>
+        <v>0.9972</v>
       </c>
       <c r="Q13" t="n">
         <v>0.6191</v>
@@ -1597,7 +1597,7 @@
         <v>0.6667</v>
       </c>
       <c r="T13" t="n">
-        <v>1</v>
+        <v>0.9949</v>
       </c>
       <c r="U13" t="n">
         <v>0.7202</v>
@@ -1609,16 +1609,16 @@
         <v>0.7042</v>
       </c>
       <c r="X13" t="n">
-        <v>0.5028</v>
+        <v>0.9549</v>
       </c>
       <c r="Y13" t="n">
-        <v>1.87</v>
+        <v>3.33</v>
       </c>
       <c r="Z13" t="n">
-        <v>18208</v>
+        <v>19328</v>
       </c>
       <c r="AA13" t="n">
-        <v>615.23</v>
+        <v>642.26</v>
       </c>
     </row>
   </sheetData>

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,16 +585,16 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7851</v>
+        <v>0.7826</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7866</v>
+        <v>0.783</v>
       </c>
       <c r="K2" t="n">
-        <v>0.733</v>
+        <v>0.7329</v>
       </c>
       <c r="L2" t="n">
-        <v>0.9</v>
+        <v>0.8957000000000001</v>
       </c>
       <c r="M2" t="n">
         <v>0.6561</v>
@@ -633,13 +633,13 @@
         <v>0.891</v>
       </c>
       <c r="Y2" t="n">
-        <v>1.45</v>
+        <v>0.95</v>
       </c>
       <c r="Z2" t="n">
         <v>48128</v>
       </c>
       <c r="AA2" t="n">
-        <v>397.07</v>
+        <v>397.74</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -585,16 +585,16 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7826</v>
+        <v>0.7851</v>
       </c>
       <c r="J2" t="n">
-        <v>0.783</v>
+        <v>0.7867</v>
       </c>
       <c r="K2" t="n">
-        <v>0.7329</v>
+        <v>0.733</v>
       </c>
       <c r="L2" t="n">
-        <v>0.8957000000000001</v>
+        <v>0.9005</v>
       </c>
       <c r="M2" t="n">
         <v>0.6561</v>
@@ -633,13 +633,13 @@
         <v>0.891</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.95</v>
+        <v>0.87</v>
       </c>
       <c r="Z2" t="n">
         <v>48128</v>
       </c>
       <c r="AA2" t="n">
-        <v>397.74</v>
+        <v>398.1</v>
       </c>
     </row>
     <row r="3">

--- a/results/link_results.xlsx
+++ b/results/link_results.xlsx
@@ -474,7 +474,7 @@
       </c>
       <c r="L1" t="inlineStr">
         <is>
-          <t>Hits@K</t>
+          <t>Hits@10pct</t>
         </is>
       </c>
       <c r="M1" t="inlineStr">
@@ -494,7 +494,7 @@
       </c>
       <c r="P1" t="inlineStr">
         <is>
-          <t>CN_Hits@K</t>
+          <t>CN_Hits@10pct</t>
         </is>
       </c>
       <c r="Q1" t="inlineStr">
@@ -514,7 +514,7 @@
       </c>
       <c r="T1" t="inlineStr">
         <is>
-          <t>AA_Hits@K</t>
+          <t>AA_Hits@10pct</t>
         </is>
       </c>
       <c r="U1" t="inlineStr">
@@ -534,7 +534,7 @@
       </c>
       <c r="X1" t="inlineStr">
         <is>
-          <t>PA_Hits@K</t>
+          <t>PA_Hits@10pct</t>
         </is>
       </c>
       <c r="Y1" t="inlineStr">
@@ -585,13 +585,13 @@
         <v>200</v>
       </c>
       <c r="I2" t="n">
-        <v>0.7851</v>
+        <v>0.7986</v>
       </c>
       <c r="J2" t="n">
-        <v>0.7867</v>
+        <v>0.8028</v>
       </c>
       <c r="K2" t="n">
-        <v>0.733</v>
+        <v>0.739</v>
       </c>
       <c r="L2" t="n">
         <v>0.9005</v>
@@ -633,13 +633,13 @@
         <v>0.891</v>
       </c>
       <c r="Y2" t="n">
-        <v>0.87</v>
+        <v>0.68</v>
       </c>
       <c r="Z2" t="n">
         <v>48128</v>
       </c>
       <c r="AA2" t="n">
-        <v>398.1</v>
+        <v>432</v>
       </c>
     </row>
     <row r="3">
@@ -674,16 +674,16 @@
         <v>200</v>
       </c>
       <c r="I3" t="n">
-        <v>0.7657</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="J3" t="n">
-        <v>0.7496</v>
+        <v>0.8659</v>
       </c>
       <c r="K3" t="n">
-        <v>0.7185</v>
+        <v>0.7813</v>
       </c>
       <c r="L3" t="n">
-        <v>0.9</v>
+        <v>0.9479</v>
       </c>
       <c r="M3" t="n">
         <v>0.6561</v>
@@ -722,13 +722,13 @@
         <v>0.891</v>
       </c>
       <c r="Y3" t="n">
-        <v>1.95</v>
+        <v>1.22</v>
       </c>
       <c r="Z3" t="n">
         <v>48256</v>
       </c>
       <c r="AA3" t="n">
-        <v>405.71</v>
+        <v>440.62</v>
       </c>
     </row>
     <row r="4">
@@ -763,16 +763,16 @@
         <v>200</v>
       </c>
       <c r="I4" t="n">
-        <v>0.7931</v>
+        <v>0.7785</v>
       </c>
       <c r="J4" t="n">
-        <v>0.7788</v>
+        <v>0.7498</v>
       </c>
       <c r="K4" t="n">
-        <v>0.7519</v>
+        <v>0.7383</v>
       </c>
       <c r="L4" t="n">
-        <v>1</v>
+        <v>0.8294</v>
       </c>
       <c r="M4" t="n">
         <v>0.6561</v>
@@ -811,13 +811,13 @@
         <v>0.891</v>
       </c>
       <c r="Y4" t="n">
-        <v>1.79</v>
+        <v>1.54</v>
       </c>
       <c r="Z4" t="n">
         <v>95008</v>
       </c>
       <c r="AA4" t="n">
-        <v>481.73</v>
+        <v>508.07</v>
       </c>
     </row>
     <row r="5">
@@ -852,16 +852,16 @@
         <v>200</v>
       </c>
       <c r="I5" t="n">
-        <v>0.7814</v>
+        <v>0.7438</v>
       </c>
       <c r="J5" t="n">
-        <v>0.8025</v>
+        <v>0.7649</v>
       </c>
       <c r="K5" t="n">
-        <v>0.7226</v>
+        <v>0.6908</v>
       </c>
       <c r="L5" t="n">
-        <v>1</v>
+        <v>0.9052</v>
       </c>
       <c r="M5" t="n">
         <v>0.6561</v>
@@ -900,13 +900,13 @@
         <v>0.891</v>
       </c>
       <c r="Y5" t="n">
-        <v>3.08</v>
+        <v>2.9</v>
       </c>
       <c r="Z5" t="n">
-        <v>49184</v>
+        <v>50240</v>
       </c>
       <c r="AA5" t="n">
-        <v>464.91</v>
+        <v>507.47</v>
       </c>
     </row>
     <row r="6">
@@ -941,16 +941,16 @@
         <v>200</v>
       </c>
       <c r="I6" t="n">
-        <v>0.802</v>
+        <v>0.8064</v>
       </c>
       <c r="J6" t="n">
-        <v>0.8135</v>
+        <v>0.819</v>
       </c>
       <c r="K6" t="n">
-        <v>0.7423999999999999</v>
+        <v>0.7322</v>
       </c>
       <c r="L6" t="n">
-        <v>1</v>
+        <v>0.9505</v>
       </c>
       <c r="M6" t="n">
         <v>0.6227</v>
@@ -989,13 +989,13 @@
         <v>0.8846000000000001</v>
       </c>
       <c r="Y6" t="n">
-        <v>0.91</v>
+        <v>0.79</v>
       </c>
       <c r="Z6" t="n">
         <v>120768</v>
       </c>
       <c r="AA6" t="n">
-        <v>429.31</v>
+        <v>464.95</v>
       </c>
     </row>
     <row r="7">
@@ -1030,16 +1030,16 @@
         <v>200</v>
       </c>
       <c r="I7" t="n">
-        <v>0.7849</v>
+        <v>0.8673999999999999</v>
       </c>
       <c r="J7" t="n">
-        <v>0.8048</v>
+        <v>0.8707</v>
       </c>
       <c r="K7" t="n">
-        <v>0.7184</v>
+        <v>0.7659</v>
       </c>
       <c r="L7" t="n">
-        <v>1</v>
+        <v>0.9725</v>
       </c>
       <c r="M7" t="n">
         <v>0.6227</v>
@@ -1078,13 +1078,13 @@
         <v>0.8846000000000001</v>
       </c>
       <c r="Y7" t="n">
-        <v>1.05</v>
+        <v>1.14</v>
       </c>
       <c r="Z7" t="n">
         <v>120896</v>
       </c>
       <c r="AA7" t="n">
-        <v>436.04</v>
+        <v>472.37</v>
       </c>
     </row>
     <row r="8">
@@ -1119,16 +1119,16 @@
         <v>200</v>
       </c>
       <c r="I8" t="n">
-        <v>0.7574</v>
+        <v>0.7685</v>
       </c>
       <c r="J8" t="n">
-        <v>0.7369</v>
+        <v>0.7503</v>
       </c>
       <c r="K8" t="n">
-        <v>0.7203000000000001</v>
+        <v>0.7252</v>
       </c>
       <c r="L8" t="n">
-        <v>1</v>
+        <v>0.8516</v>
       </c>
       <c r="M8" t="n">
         <v>0.6227</v>
@@ -1167,13 +1167,13 @@
         <v>0.8846000000000001</v>
       </c>
       <c r="Y8" t="n">
-        <v>4.43</v>
+        <v>4.92</v>
       </c>
       <c r="Z8" t="n">
         <v>240288</v>
       </c>
       <c r="AA8" t="n">
-        <v>634.96</v>
+        <v>663.33</v>
       </c>
     </row>
     <row r="9">
@@ -1208,16 +1208,16 @@
         <v>200</v>
       </c>
       <c r="I9" t="n">
-        <v>0.716</v>
+        <v>0.7299</v>
       </c>
       <c r="J9" t="n">
-        <v>0.7149</v>
+        <v>0.7193000000000001</v>
       </c>
       <c r="K9" t="n">
-        <v>0.702</v>
+        <v>0.7010999999999999</v>
       </c>
       <c r="L9" t="n">
-        <v>1</v>
+        <v>0.8242</v>
       </c>
       <c r="M9" t="n">
         <v>0.6227</v>
@@ -1256,13 +1256,13 @@
         <v>0.8846000000000001</v>
       </c>
       <c r="Y9" t="n">
-        <v>4.06</v>
+        <v>4.42</v>
       </c>
       <c r="Z9" t="n">
-        <v>121824</v>
+        <v>122880</v>
       </c>
       <c r="AA9" t="n">
-        <v>622.8</v>
+        <v>708.46</v>
       </c>
     </row>
     <row r="10">
@@ -1297,16 +1297,16 @@
         <v>200</v>
       </c>
       <c r="I10" t="n">
-        <v>0.9287</v>
+        <v>0.9340000000000001</v>
       </c>
       <c r="J10" t="n">
-        <v>0.9351</v>
+        <v>0.9392</v>
       </c>
       <c r="K10" t="n">
-        <v>0.802</v>
+        <v>0.8021</v>
       </c>
       <c r="L10" t="n">
-        <v>1</v>
+        <v>0.9893</v>
       </c>
       <c r="M10" t="n">
         <v>0.619</v>
@@ -1345,13 +1345,13 @@
         <v>0.9549</v>
       </c>
       <c r="Y10" t="n">
-        <v>3.74</v>
+        <v>4.05</v>
       </c>
       <c r="Z10" t="n">
         <v>18272</v>
       </c>
       <c r="AA10" t="n">
-        <v>516.29</v>
+        <v>529.91</v>
       </c>
     </row>
     <row r="11">
@@ -1386,16 +1386,16 @@
         <v>200</v>
       </c>
       <c r="I11" t="n">
-        <v>0.8826000000000001</v>
+        <v>0.9222</v>
       </c>
       <c r="J11" t="n">
-        <v>0.8771</v>
+        <v>0.9107</v>
       </c>
       <c r="K11" t="n">
-        <v>0.7786999999999999</v>
+        <v>0.8186</v>
       </c>
       <c r="L11" t="n">
-        <v>0.9</v>
+        <v>0.9639</v>
       </c>
       <c r="M11" t="n">
         <v>0.619</v>
@@ -1434,13 +1434,13 @@
         <v>0.9549</v>
       </c>
       <c r="Y11" t="n">
-        <v>8.550000000000001</v>
+        <v>8.949999999999999</v>
       </c>
       <c r="Z11" t="n">
         <v>18400</v>
       </c>
       <c r="AA11" t="n">
-        <v>572.59</v>
+        <v>558.48</v>
       </c>
     </row>
     <row r="12">
@@ -1475,16 +1475,16 @@
         <v>200</v>
       </c>
       <c r="I12" t="n">
-        <v>0.8569</v>
+        <v>0.8618</v>
       </c>
       <c r="J12" t="n">
-        <v>0.8622</v>
+        <v>0.8683999999999999</v>
       </c>
       <c r="K12" t="n">
-        <v>0.7664</v>
+        <v>0.7708</v>
       </c>
       <c r="L12" t="n">
-        <v>0.9</v>
+        <v>0.9752</v>
       </c>
       <c r="M12" t="n">
         <v>0.619</v>
@@ -1523,13 +1523,13 @@
         <v>0.9549</v>
       </c>
       <c r="Y12" t="n">
-        <v>7.19</v>
+        <v>9.01</v>
       </c>
       <c r="Z12" t="n">
         <v>35296</v>
       </c>
       <c r="AA12" t="n">
-        <v>688.35</v>
+        <v>750.6</v>
       </c>
     </row>
     <row r="13">
@@ -1564,16 +1564,16 @@
         <v>200</v>
       </c>
       <c r="I13" t="n">
-        <v>0.7462</v>
+        <v>0.7616000000000001</v>
       </c>
       <c r="J13" t="n">
-        <v>0.8159</v>
+        <v>0.8250999999999999</v>
       </c>
       <c r="K13" t="n">
-        <v>0.662</v>
+        <v>0.6738</v>
       </c>
       <c r="L13" t="n">
-        <v>1</v>
+        <v>0.9836</v>
       </c>
       <c r="M13" t="n">
         <v>0.619</v>
@@ -1612,13 +1612,13 @@
         <v>0.9549</v>
       </c>
       <c r="Y13" t="n">
-        <v>3.33</v>
+        <v>3.41</v>
       </c>
       <c r="Z13" t="n">
-        <v>19328</v>
+        <v>20384</v>
       </c>
       <c r="AA13" t="n">
-        <v>642.26</v>
+        <v>811.77</v>
       </c>
     </row>
   </sheetData>
